--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B3" t="n">
-        <v>58508</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>482446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>58508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126054122</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R6" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R7" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>126056378</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>126054906</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126054128</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126054282</v>
+        <v>126054736</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,14 +1669,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482411</v>
+        <v>482451</v>
       </c>
       <c r="R11" t="n">
-        <v>6950711</v>
+        <v>6950641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126054736</v>
+        <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482451</v>
+        <v>482711</v>
       </c>
       <c r="R12" t="n">
-        <v>6950641</v>
+        <v>6950560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,22 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126055171</v>
+        <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482711</v>
+        <v>482411</v>
       </c>
       <c r="R13" t="n">
-        <v>6950560</v>
+        <v>6950711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
         <v>126053933</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>126054728</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>126054793</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126054838</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B20" t="n">
-        <v>80072</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R20" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B21" t="n">
-        <v>78727</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>126055617</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R21" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>58508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R3" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B4" t="n">
-        <v>58508</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R6" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R7" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126054736</v>
+        <v>126055171</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482451</v>
+        <v>482711</v>
       </c>
       <c r="R11" t="n">
-        <v>6950641</v>
+        <v>6950560</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126055171</v>
+        <v>126054736</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482711</v>
+        <v>482451</v>
       </c>
       <c r="R12" t="n">
-        <v>6950560</v>
+        <v>6950641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,12 +1840,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R6" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R7" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054484</v>
+        <v>126055235</v>
       </c>
       <c r="B2" t="n">
-        <v>58508</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126055235</v>
+        <v>126053969</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950535</v>
+        <v>6950790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126053969</v>
+        <v>126054484</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>58508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950790</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R6" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R7" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>58509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R3" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B4" t="n">
-        <v>58508</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126054122</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R6" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R7" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>126056378</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>126054906</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126054128</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126055171</v>
+        <v>126054736</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482711</v>
+        <v>482451</v>
       </c>
       <c r="R11" t="n">
-        <v>6950560</v>
+        <v>6950641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126054736</v>
+        <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482451</v>
+        <v>482711</v>
       </c>
       <c r="R12" t="n">
-        <v>6950641</v>
+        <v>6950560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,12 +1840,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
         <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>126053933</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>126054728</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>126054793</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126054838</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>126054254</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>126055981</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>126055617</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R20" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>80077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054484</v>
+        <v>126055235</v>
       </c>
       <c r="B2" t="n">
-        <v>58509</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126055235</v>
+        <v>126053969</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950535</v>
+        <v>6950790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126053969</v>
+        <v>126054484</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>58509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950790</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R6" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R7" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126055171</v>
+        <v>126054282</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482711</v>
+        <v>482411</v>
       </c>
       <c r="R12" t="n">
-        <v>6950560</v>
+        <v>6950711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126054282</v>
+        <v>126055171</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482411</v>
+        <v>482711</v>
       </c>
       <c r="R13" t="n">
-        <v>6950711</v>
+        <v>6950560</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053933</v>
+        <v>126054728</v>
       </c>
       <c r="B14" t="n">
         <v>80076</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482434</v>
+        <v>482452</v>
       </c>
       <c r="R14" t="n">
-        <v>6950766</v>
+        <v>6950615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126054728</v>
+        <v>126053933</v>
       </c>
       <c r="B15" t="n">
         <v>80076</v>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482452</v>
+        <v>482434</v>
       </c>
       <c r="R15" t="n">
-        <v>6950615</v>
+        <v>6950766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126055865</v>
+        <v>126054375</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482622</v>
+        <v>482448</v>
       </c>
       <c r="R18" t="n">
-        <v>6950725</v>
+        <v>6950690</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126054375</v>
+        <v>126055865</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482448</v>
+        <v>482622</v>
       </c>
       <c r="R19" t="n">
-        <v>6950690</v>
+        <v>6950725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B21" t="n">
-        <v>80077</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R21" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126054375</v>
+        <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482448</v>
+        <v>482622</v>
       </c>
       <c r="R18" t="n">
-        <v>6950690</v>
+        <v>6950725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126055865</v>
+        <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482622</v>
+        <v>482448</v>
       </c>
       <c r="R19" t="n">
-        <v>6950725</v>
+        <v>6950690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R6" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R7" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126054282</v>
+        <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482411</v>
+        <v>482711</v>
       </c>
       <c r="R12" t="n">
-        <v>6950711</v>
+        <v>6950560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126055171</v>
+        <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482711</v>
+        <v>482411</v>
       </c>
       <c r="R13" t="n">
-        <v>6950560</v>
+        <v>6950711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126054728</v>
+        <v>126053933</v>
       </c>
       <c r="B14" t="n">
         <v>80076</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482452</v>
+        <v>482434</v>
       </c>
       <c r="R14" t="n">
-        <v>6950615</v>
+        <v>6950766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126053933</v>
+        <v>126054728</v>
       </c>
       <c r="B15" t="n">
         <v>80076</v>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482434</v>
+        <v>482452</v>
       </c>
       <c r="R15" t="n">
-        <v>6950766</v>
+        <v>6950615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>58513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R3" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B4" t="n">
-        <v>58509</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126054122</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126056378</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>126054906</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126054128</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126054736</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>126053933</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>126054728</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>126054793</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126054838</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>126054254</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>126055981</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>126055617</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B2" t="n">
-        <v>58513</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126053969</v>
+        <v>126054484</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>58513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950790</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B6" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R6" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R7" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126055171</v>
+        <v>126054282</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482711</v>
+        <v>482411</v>
       </c>
       <c r="R12" t="n">
-        <v>6950560</v>
+        <v>6950711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126054282</v>
+        <v>126055171</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482411</v>
+        <v>482711</v>
       </c>
       <c r="R13" t="n">
-        <v>6950711</v>
+        <v>6950560</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053933</v>
+        <v>126054728</v>
       </c>
       <c r="B14" t="n">
         <v>80080</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482434</v>
+        <v>482452</v>
       </c>
       <c r="R14" t="n">
-        <v>6950766</v>
+        <v>6950615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126054728</v>
+        <v>126053933</v>
       </c>
       <c r="B15" t="n">
         <v>80080</v>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482452</v>
+        <v>482434</v>
       </c>
       <c r="R15" t="n">
-        <v>6950615</v>
+        <v>6950766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126055865</v>
+        <v>126054375</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482622</v>
+        <v>482448</v>
       </c>
       <c r="R18" t="n">
-        <v>6950725</v>
+        <v>6950690</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126054375</v>
+        <v>126055865</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482448</v>
+        <v>482622</v>
       </c>
       <c r="R19" t="n">
-        <v>6950690</v>
+        <v>6950725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R20" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>80081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126055235</v>
+        <v>126053969</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950535</v>
+        <v>6950790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126054322</v>
+        <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482394</v>
+        <v>482578</v>
       </c>
       <c r="R6" t="n">
-        <v>6950719</v>
+        <v>6950832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126056319</v>
+        <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482578</v>
+        <v>482394</v>
       </c>
       <c r="R7" t="n">
-        <v>6950832</v>
+        <v>6950719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126054282</v>
+        <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482411</v>
+        <v>482711</v>
       </c>
       <c r="R12" t="n">
-        <v>6950711</v>
+        <v>6950560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126055171</v>
+        <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482711</v>
+        <v>482411</v>
       </c>
       <c r="R13" t="n">
-        <v>6950560</v>
+        <v>6950711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126054728</v>
+        <v>126053933</v>
       </c>
       <c r="B14" t="n">
         <v>80080</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482452</v>
+        <v>482434</v>
       </c>
       <c r="R14" t="n">
-        <v>6950615</v>
+        <v>6950766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126053933</v>
+        <v>126054728</v>
       </c>
       <c r="B15" t="n">
         <v>80080</v>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482434</v>
+        <v>482452</v>
       </c>
       <c r="R15" t="n">
-        <v>6950766</v>
+        <v>6950615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126054375</v>
+        <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482448</v>
+        <v>482622</v>
       </c>
       <c r="R18" t="n">
-        <v>6950690</v>
+        <v>6950725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126055865</v>
+        <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482622</v>
+        <v>482448</v>
       </c>
       <c r="R19" t="n">
-        <v>6950725</v>
+        <v>6950690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>58516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126053969</v>
+        <v>126055235</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R3" t="n">
-        <v>6950790</v>
+        <v>6950535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126054484</v>
+        <v>126053969</v>
       </c>
       <c r="B4" t="n">
-        <v>58513</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>482446</v>
       </c>
       <c r="R4" t="n">
-        <v>6950715</v>
+        <v>6950790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126054122</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126056319</v>
       </c>
       <c r="B6" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126054322</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>126056378</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>126054906</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126054128</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126054736</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126055171</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>126054282</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>126053933</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>126054728</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>126054793</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126054838</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>126055865</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126054375</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126055981</v>
+        <v>126054254</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>80084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482618</v>
+        <v>482394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950723</v>
+        <v>6950719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126054254</v>
+        <v>126055981</v>
       </c>
       <c r="B21" t="n">
-        <v>80081</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482394</v>
+        <v>482618</v>
       </c>
       <c r="R21" t="n">
-        <v>6950719</v>
+        <v>6950723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>126055617</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054484</v>
+        <v>126055235</v>
       </c>
       <c r="B2" t="n">
-        <v>58516</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>58516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054484</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>58516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482446</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054484</v>
+        <v>126055235</v>
       </c>
       <c r="B3" t="n">
-        <v>58516</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482706</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 27957-2025 artfynd.xlsx
+++ b/artfynd/A 27957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126055235</v>
+        <v>126054254</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482706</v>
+        <v>482394</v>
       </c>
       <c r="R2" t="n">
-        <v>6950535</v>
+        <v>6950719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054484</v>
+        <v>126054128</v>
       </c>
       <c r="B3" t="n">
-        <v>58516</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482446</v>
+        <v>482447</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950791</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,14 +862,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126053969</v>
+        <v>126054375</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482446</v>
+        <v>482448</v>
       </c>
       <c r="R4" t="n">
-        <v>6950790</v>
+        <v>6950690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,14 +969,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -984,57 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126054122</v>
+        <v>126054793</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482421</v>
+        <v>482451</v>
       </c>
       <c r="R5" t="n">
-        <v>6950760</v>
+        <v>6950641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,57 +1091,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126056319</v>
+        <v>126054838</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482578</v>
+        <v>482462</v>
       </c>
       <c r="R6" t="n">
-        <v>6950832</v>
+        <v>6950575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,57 +1198,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126054322</v>
+        <v>126054906</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482394</v>
+        <v>482464</v>
       </c>
       <c r="R7" t="n">
-        <v>6950719</v>
+        <v>6950596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,45 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126056378</v>
+        <v>126055171</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482582</v>
+        <v>482711</v>
       </c>
       <c r="R8" t="n">
-        <v>6950829</v>
+        <v>6950560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,26 +1412,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126054906</v>
+        <v>126055235</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482464</v>
+        <v>482706</v>
       </c>
       <c r="R9" t="n">
-        <v>6950596</v>
+        <v>6950535</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126054128</v>
+        <v>126055865</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,34 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482447</v>
+        <v>482622</v>
       </c>
       <c r="R10" t="n">
-        <v>6950791</v>
+        <v>6950725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,14 +1611,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1626,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126054736</v>
+        <v>126056319</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482451</v>
+        <v>482578</v>
       </c>
       <c r="R11" t="n">
-        <v>6950641</v>
+        <v>6950832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126055171</v>
+        <v>124411366</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,37 +1756,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482711</v>
+        <v>482651</v>
       </c>
       <c r="R12" t="n">
-        <v>6950560</v>
+        <v>6951035</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1810,22 +1810,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126054282</v>
+        <v>126053933</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482411</v>
+        <v>482434</v>
       </c>
       <c r="R13" t="n">
-        <v>6950711</v>
+        <v>6950766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053933</v>
+        <v>126053969</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482434</v>
+        <v>482446</v>
       </c>
       <c r="R14" t="n">
-        <v>6950766</v>
+        <v>6950790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,14 +2029,14 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2054,22 +2044,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126054728</v>
+        <v>126054122</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,14 +2087,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482452</v>
+        <v>482421</v>
       </c>
       <c r="R15" t="n">
-        <v>6950615</v>
+        <v>6950760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126054793</v>
+        <v>126054282</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,34 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482451</v>
+        <v>482411</v>
       </c>
       <c r="R16" t="n">
-        <v>6950641</v>
+        <v>6950711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,22 +2258,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126054838</v>
+        <v>126054322</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högboda, Högboda, Jmt</t>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482462</v>
+        <v>482394</v>
       </c>
       <c r="R17" t="n">
-        <v>6950575</v>
+        <v>6950719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,22 +2365,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126055865</v>
+        <v>126054728</v>
       </c>
       <c r="B18" t="n">
-        <v>78738</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482622</v>
+        <v>482452</v>
       </c>
       <c r="R18" t="n">
-        <v>6950725</v>
+        <v>6950615</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126054375</v>
+        <v>126054736</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482448</v>
+        <v>482451</v>
       </c>
       <c r="R19" t="n">
-        <v>6950690</v>
+        <v>6950641</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,22 +2579,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126054254</v>
+        <v>126055617</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+          <t>Högboda, Högboda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482394</v>
+        <v>482668</v>
       </c>
       <c r="R20" t="n">
-        <v>6950719</v>
+        <v>6950660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,44 +2686,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126055981</v>
+        <v>126054484</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>58817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482618</v>
+        <v>482446</v>
       </c>
       <c r="R21" t="n">
-        <v>6950723</v>
+        <v>6950715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126055617</v>
+        <v>126055981</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482668</v>
+        <v>482618</v>
       </c>
       <c r="R22" t="n">
-        <v>6950660</v>
+        <v>6950723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,15 +2900,122 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126056378</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Hackåstjärnen, Lill-Hackåstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>482582</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6950829</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
